--- a/docs/CDM/common_datamodel.xlsx
+++ b/docs/CDM/common_datamodel.xlsx
@@ -556,7 +556,8 @@
 v0.0.6. 2024.10.16 - Revisión y ajuste con referencia al codebook final. 
 v0.1.0. 2025.01.16 - Revisión y actualizacion de los campos sin completar.
 v0.1.1.2025.01.18 - Ajuste de formatos de diferentes campos
-v0.1.3.2025.12.02 - Ajustes menores de formato en variables booleanas y comentarios para algunas variables</t>
+v0.1.3.2025.12.02 - Ajustes menores de formato en variables booleanas y comentarios para algunas variables
+v.0.1.4.2025.12.18 - Reglas de validación y criterios de exclusión actualizadas</t>
         </is>
       </c>
     </row>
@@ -632,7 +633,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Personas sin uso de atencion primaria los dos anos previos al 2012, es decir,  2010-2011. </t>
+          <t>Personas sin uso de atencion primaria los dos anos previos al 2012, es decir,  2010-2011.
+Fecha de nacimiento anterior al 1917-01-01</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1840,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Seguir diccionario "dicc_cie_ciap_snack_final". En "CHRONIC_KIDNEY_DISEASE" incluir también personas a partir del Filtrado Glomerular. En "COPD, EMPHYSEMA, CHRONIC BRONCHITIS" incluir personas con uso de triotopio/ipatropio más de 3 meses.  En "HEART FAILURE" incluir también personas con uso de furosemida, torasemida o bumetanida más de 3 meses.</t>
+          <t>Seguir diccionario "dicc_cie_ciap_snack_final". En "CHRONIC_KIDNEY_DISEASE" incluir también personas a partir del Filtrado Glomerular. En "COPD_EMPHYSEMA_CHRONIC_BRONCHITIS" incluir personas con uso de triotopio/ipatropio más de 3 meses.  En "HEART_FAILURE" incluir también personas con uso de furosemida, torasemida o bumetanida más de 3 meses.</t>
         </is>
       </c>
     </row>
